--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9104,0.0696,0.0121,0.0018</t>
-  </si>
-  <si>
-    <t>0.8749,0.0690,0.0062,0.0043</t>
-  </si>
-  <si>
-    <t>0.9355,0.0268,0.0024,0.0035</t>
-  </si>
-  <si>
-    <t>0.9657,0.0110,0.0015,0.0020</t>
-  </si>
-  <si>
-    <t>0.8430,0.1871,0.0057,0.0011</t>
-  </si>
-  <si>
-    <t>0.9239,0.0651,0.0011,0.0010</t>
-  </si>
-  <si>
-    <t>0.8972,0.0867,0.0023,0.0012</t>
-  </si>
-  <si>
-    <t>0.9276,0.0446,0.0043,0.0023</t>
-  </si>
-  <si>
-    <t>0.8664,0.1610,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.8476,0.1987,0.0048,0.0010</t>
-  </si>
-  <si>
-    <t>0.8006,0.2008,0.0058,0.0020</t>
-  </si>
-  <si>
-    <t>0.8222,0.2485,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.9847,0.0067,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.9921,0.0016,0.0039,0.0001</t>
-  </si>
-  <si>
-    <t>0.9394,0.0265,0.0307,0.0008</t>
-  </si>
-  <si>
-    <t>0.9417,0.0122,0.0598,0.0016</t>
-  </si>
-  <si>
-    <t>0.8990,0.0816,0.0216,0.0013</t>
-  </si>
-  <si>
-    <t>0.2911,0.8367,0.0063,0.0003</t>
-  </si>
-  <si>
-    <t>0.5987,0.5682,0.0045,0.0005</t>
-  </si>
-  <si>
-    <t>0.9075,0.1214,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.3644,0.7857,0.0045,0.0006</t>
-  </si>
-  <si>
-    <t>0.4308,0.7594,0.0039,0.0001</t>
-  </si>
-  <si>
-    <t>0.9807,0.0039,0.0123,0.0005</t>
-  </si>
-  <si>
-    <t>0.9859,0.0018,0.0116,0.0001</t>
-  </si>
-  <si>
-    <t>0.9751,0.0014,0.0359,0.0006</t>
-  </si>
-  <si>
-    <t>0.9882,0.0013,0.0097,0.0003</t>
-  </si>
-  <si>
-    <t>0.9830,0.0036,0.0126,0.0002</t>
-  </si>
-  <si>
-    <t>0.9521,0.0196,0.0221,0.0007</t>
-  </si>
-  <si>
-    <t>0.8580,0.0034,0.2259,0.0008</t>
-  </si>
-  <si>
-    <t>0.9866,0.0105,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.8303,0.1549,0.0101,0.0023</t>
-  </si>
-  <si>
-    <t>0.0110,0.5142,0.9729,0.0023</t>
-  </si>
-  <si>
-    <t>0.6154,0.4146,0.0225,0.0002</t>
-  </si>
-  <si>
-    <t>0.9299,0.0552,0.0047,0.0010</t>
-  </si>
-  <si>
-    <t>0.8741,0.1122,0.0020,0.0012</t>
-  </si>
-  <si>
-    <t>0.7996,0.2287,0.0044,0.0011</t>
-  </si>
-  <si>
-    <t>0.9630,0.0378,0.0038,0.0003</t>
-  </si>
-  <si>
-    <t>0.7426,0.1847,0.0240,0.0008</t>
-  </si>
-  <si>
-    <t>0.9200,0.0038,0.1596,0.0022</t>
-  </si>
-  <si>
-    <t>0.9478,0.0035,0.0901,0.0004</t>
-  </si>
-  <si>
-    <t>0.9851,0.0005,0.0193,0.0005</t>
-  </si>
-  <si>
-    <t>0.9800,0.0021,0.0260,0.0004</t>
-  </si>
-  <si>
-    <t>0.5539,0.3176,0.0166,0.0001</t>
-  </si>
-  <si>
-    <t>0.9905,0.0012,0.0099,0.0001</t>
-  </si>
-  <si>
-    <t>0.9179,0.0497,0.0215,0.0040</t>
-  </si>
-  <si>
-    <t>0.9192,0.0696,0.0069,0.0002</t>
-  </si>
-  <si>
-    <t>0.9461,0.0510,0.0069,0.0002</t>
-  </si>
-  <si>
-    <t>0.9030,0.0820,0.0087,0.0001</t>
-  </si>
-  <si>
-    <t>0.0747,0.0110,0.9395,0.0003</t>
-  </si>
-  <si>
-    <t>0.2795,0.0305,0.7851,0.0059</t>
-  </si>
-  <si>
-    <t>0.9775,0.0022,0.0255,0.0003</t>
-  </si>
-  <si>
-    <t>0.7363,0.0271,0.3680,0.0028</t>
-  </si>
-  <si>
-    <t>0.4627,0.0228,0.5215,0.0005</t>
-  </si>
-  <si>
-    <t>0.8544,0.0154,0.1446,0.0005</t>
-  </si>
-  <si>
-    <t>0.9329,0.0601,0.0034,0.0013</t>
-  </si>
-  <si>
-    <t>0.9107,0.0459,0.0028,0.0036</t>
-  </si>
-  <si>
-    <t>0.9058,0.0726,0.0036,0.0020</t>
-  </si>
-  <si>
-    <t>0.6215,0.1871,0.2760,0.0084</t>
-  </si>
-  <si>
-    <t>0.9065,0.0691,0.0033,0.0016</t>
-  </si>
-  <si>
-    <t>0.9432,0.0330,0.0039,0.0024</t>
-  </si>
-  <si>
-    <t>0.9452,0.0671,0.0025,0.0004</t>
-  </si>
-  <si>
-    <t>0.1343,0.2202,0.7050,0.0021</t>
-  </si>
-  <si>
-    <t>0.2059,0.0091,0.9006,0.0019</t>
-  </si>
-  <si>
-    <t>0.6379,0.0153,0.4886,0.0014</t>
-  </si>
-  <si>
-    <t>0.5294,0.0390,0.5142,0.0005</t>
-  </si>
-  <si>
-    <t>0.7835,0.0028,0.4094,0.0009</t>
-  </si>
-  <si>
-    <t>0.2341,0.8433,0.0060,0.0001</t>
-  </si>
-  <si>
-    <t>0.2853,0.8318,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9402,0.0415,0.0139,0.0005</t>
-  </si>
-  <si>
-    <t>0.9520,0.0384,0.0035,0.0005</t>
-  </si>
-  <si>
-    <t>0.0203,0.8419,0.8453,0.0011</t>
-  </si>
-  <si>
-    <t>0.8161,0.0557,0.1109,0.0008</t>
-  </si>
-  <si>
-    <t>0.8454,0.0263,0.1122,0.0005</t>
-  </si>
-  <si>
-    <t>0.0617,0.9575,0.0060,0.0000</t>
-  </si>
-  <si>
-    <t>0.5271,0.3404,0.1282,0.0015</t>
-  </si>
-  <si>
-    <t>0.9666,0.0106,0.0063,0.0025</t>
-  </si>
-  <si>
-    <t>0.9652,0.0059,0.0047,0.0071</t>
-  </si>
-  <si>
-    <t>0.9074,0.0324,0.0155,0.0088</t>
-  </si>
-  <si>
-    <t>0.9669,0.0100,0.0076,0.0015</t>
-  </si>
-  <si>
-    <t>0.8840,0.0776,0.0157,0.0087</t>
-  </si>
-  <si>
-    <t>0.9155,0.0289,0.0211,0.0136</t>
-  </si>
-  <si>
-    <t>0.9522,0.0087,0.0532,0.0004</t>
-  </si>
-  <si>
-    <t>0.8515,0.0229,0.1338,0.0003</t>
-  </si>
-  <si>
-    <t>0.4717,0.1186,0.4436,0.0026</t>
-  </si>
-  <si>
-    <t>0.9158,0.0195,0.0414,0.0003</t>
-  </si>
-  <si>
-    <t>0.5563,0.2953,0.1164,0.0008</t>
-  </si>
-  <si>
-    <t>0.9354,0.0341,0.0063,0.0000</t>
-  </si>
-  <si>
-    <t>0.9114,0.1004,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.9708,0.0315,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9574,0.0393,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.9658,0.0233,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9180,0.0533,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9046,0.1080,0.0031,0.0011</t>
-  </si>
-  <si>
-    <t>0.9277,0.0650,0.0027,0.0017</t>
-  </si>
-  <si>
-    <t>0.7635,0.2264,0.0074,0.0029</t>
-  </si>
-  <si>
-    <t>0.8997,0.0715,0.0050,0.0027</t>
-  </si>
-  <si>
-    <t>0.7962,0.1841,0.0049,0.0026</t>
-  </si>
-  <si>
-    <t>0.9598,0.0231,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.9312,0.0660,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.9608,0.0264,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.9404,0.0637,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.8767,0.1151,0.0049,0.0016</t>
-  </si>
-  <si>
-    <t>0.9720,0.0226,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.1396,0.0191,0.9182,0.0016</t>
-  </si>
-  <si>
-    <t>0.9599,0.0107,0.0214,0.0005</t>
-  </si>
-  <si>
-    <t>0.9913,0.0013,0.0053,0.0002</t>
-  </si>
-  <si>
-    <t>0.9614,0.0069,0.0352,0.0003</t>
-  </si>
-  <si>
-    <t>0.1902,0.8895,0.0051,0.0005</t>
-  </si>
-  <si>
-    <t>0.5336,0.6346,0.0080,0.0004</t>
-  </si>
-  <si>
-    <t>0.5174,0.6127,0.0173,0.0006</t>
-  </si>
-  <si>
-    <t>0.9637,0.0290,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.6572,0.5455,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.6554,0.4697,0.0066,0.0007</t>
-  </si>
-  <si>
-    <t>0.8569,0.2383,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.9744,0.0115,0.0075,0.0004</t>
-  </si>
-  <si>
-    <t>0.6488,0.1201,0.2223,0.0053</t>
-  </si>
-  <si>
-    <t>0.9262,0.0529,0.0109,0.0005</t>
-  </si>
-  <si>
-    <t>0.9466,0.0404,0.0078,0.0002</t>
-  </si>
-  <si>
-    <t>0.9449,0.0292,0.0131,0.0028</t>
-  </si>
-  <si>
-    <t>0.9698,0.0359,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.5763,0.5556,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.8882,0.1253,0.0082,0.0005</t>
-  </si>
-  <si>
-    <t>0.2220,0.3216,0.1905,0.0003</t>
-  </si>
-  <si>
-    <t>0.9259,0.1132,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.9744,0.0176,0.0028,0.0005</t>
-  </si>
-  <si>
-    <t>0.8252,0.2861,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.9653,0.0346,0.0035,0.0003</t>
-  </si>
-  <si>
-    <t>0.7796,0.2415,0.0067,0.0017</t>
-  </si>
-  <si>
-    <t>0.9461,0.0459,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.8139,0.1917,0.0068,0.0016</t>
-  </si>
-  <si>
-    <t>0.8921,0.0913,0.0031,0.0022</t>
-  </si>
-  <si>
-    <t>0.8996,0.0733,0.0061,0.0027</t>
-  </si>
-  <si>
-    <t>0.9438,0.0520,0.0029,0.0006</t>
-  </si>
-  <si>
-    <t>0.9361,0.0582,0.0026,0.0015</t>
-  </si>
-  <si>
-    <t>0.9693,0.0024,0.0559,0.0002</t>
-  </si>
-  <si>
-    <t>0.8378,0.0203,0.2198,0.0012</t>
-  </si>
-  <si>
-    <t>0.8750,0.0115,0.1167,0.0006</t>
-  </si>
-  <si>
-    <t>0.9794,0.0019,0.0240,0.0003</t>
-  </si>
-  <si>
-    <t>0.9739,0.0154,0.0047,0.0003</t>
-  </si>
-  <si>
-    <t>0.9458,0.0176,0.0299,0.0008</t>
-  </si>
-  <si>
-    <t>0.8552,0.1013,0.0384,0.0018</t>
-  </si>
-  <si>
-    <t>0.9795,0.0099,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.9724,0.0118,0.0038,0.0013</t>
-  </si>
-  <si>
-    <t>0.8566,0.0255,0.0806,0.0165</t>
-  </si>
-  <si>
-    <t>0.9194,0.0237,0.0332,0.0110</t>
-  </si>
-  <si>
-    <t>0.9859,0.0027,0.0022,0.0015</t>
-  </si>
-  <si>
-    <t>0.0885,0.7987,0.4239,0.0006</t>
-  </si>
-  <si>
-    <t>0.9326,0.0598,0.0023,0.0012</t>
-  </si>
-  <si>
-    <t>0.8739,0.2272,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.9498,0.0287,0.0015,0.0019</t>
-  </si>
-  <si>
-    <t>0.6148,0.4543,0.0112,0.0018</t>
-  </si>
-  <si>
-    <t>0.8578,0.0872,0.0095,0.0043</t>
-  </si>
-  <si>
-    <t>0.8466,0.0985,0.0118,0.0055</t>
-  </si>
-  <si>
-    <t>0.8111,0.1369,0.0272,0.0101</t>
-  </si>
-  <si>
-    <t>0.2957,0.2981,0.6840,0.0226</t>
-  </si>
-  <si>
-    <t>0.9629,0.0196,0.0047,0.0008</t>
-  </si>
-  <si>
-    <t>0.5675,0.4360,0.0092,0.0027</t>
-  </si>
-  <si>
-    <t>0.7769,0.2659,0.0092,0.0006</t>
-  </si>
-  <si>
-    <t>0.9662,0.0142,0.0022,0.0012</t>
-  </si>
-  <si>
-    <t>0.8887,0.1263,0.0100,0.0005</t>
-  </si>
-  <si>
-    <t>0.9577,0.0413,0.0028,0.0004</t>
-  </si>
-  <si>
-    <t>0.9112,0.0784,0.0170,0.0010</t>
-  </si>
-  <si>
-    <t>0.9922,0.0029,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9491,0.0288,0.0014,0.0020</t>
-  </si>
-  <si>
-    <t>0.9209,0.0586,0.0044,0.0022</t>
-  </si>
-  <si>
-    <t>0.9600,0.0218,0.0032,0.0020</t>
-  </si>
-  <si>
-    <t>0.8600,0.1233,0.0154,0.0045</t>
-  </si>
-  <si>
-    <t>0.9013,0.0884,0.0021,0.0015</t>
-  </si>
-  <si>
-    <t>0.9766,0.0129,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9809,0.0070,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9685,0.0190,0.0017,0.0011</t>
-  </si>
-  <si>
-    <t>0.8886,0.1258,0.0064,0.0012</t>
-  </si>
-  <si>
-    <t>0.9163,0.0994,0.0031,0.0005</t>
-  </si>
-  <si>
-    <t>0.9634,0.0243,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.6488,0.1670,0.1889,0.0039</t>
-  </si>
-  <si>
-    <t>0.9219,0.0830,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.9442,0.0414,0.0043,0.0018</t>
-  </si>
-  <si>
-    <t>0.9236,0.0956,0.0035,0.0008</t>
-  </si>
-  <si>
-    <t>0.5705,0.5576,0.0103,0.0013</t>
-  </si>
-  <si>
-    <t>0.1261,0.0387,0.9015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9046,0.1136,0.0061,0.0005</t>
-  </si>
-  <si>
-    <t>0.9077,0.0175,0.0899,0.0009</t>
-  </si>
-  <si>
-    <t>0.7644,0.0033,0.4257,0.0007</t>
-  </si>
-  <si>
-    <t>0.9088,0.0192,0.0862,0.0014</t>
-  </si>
-  <si>
-    <t>0.6345,0.0113,0.5120,0.0001</t>
-  </si>
-  <si>
-    <t>0.8637,0.0154,0.1569,0.0030</t>
-  </si>
-  <si>
-    <t>0.8777,0.0078,0.1519,0.0010</t>
-  </si>
-  <si>
-    <t>0.5384,0.1282,0.4840,0.0099</t>
-  </si>
-  <si>
-    <t>0.9802,0.0053,0.0082,0.0003</t>
-  </si>
-  <si>
-    <t>0.9358,0.0163,0.0427,0.0015</t>
-  </si>
-  <si>
-    <t>0.9208,0.0343,0.0318,0.0018</t>
-  </si>
-  <si>
-    <t>0.8645,0.1078,0.0185,0.0004</t>
-  </si>
-  <si>
-    <t>0.8682,0.1200,0.0192,0.0003</t>
-  </si>
-  <si>
-    <t>0.9602,0.0301,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.9475,0.0211,0.0152,0.0010</t>
-  </si>
-  <si>
-    <t>0.9771,0.0060,0.0081,0.0004</t>
-  </si>
-  <si>
-    <t>0.9076,0.1065,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.9205,0.1115,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.3638,0.7862,0.0065,0.0004</t>
-  </si>
-  <si>
-    <t>0.9536,0.0483,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.7680,0.2238,0.0306,0.0050</t>
-  </si>
-  <si>
-    <t>0.9702,0.0136,0.0070,0.0001</t>
-  </si>
-  <si>
-    <t>0.9181,0.0438,0.0323,0.0009</t>
-  </si>
-  <si>
-    <t>0.9419,0.0219,0.0299,0.0015</t>
-  </si>
-  <si>
-    <t>0.9608,0.0137,0.0167,0.0015</t>
-  </si>
-  <si>
-    <t>0.9132,0.0217,0.0579,0.0028</t>
-  </si>
-  <si>
-    <t>0.3040,0.1459,0.5885,0.0100</t>
-  </si>
-  <si>
-    <t>0.8978,0.0186,0.1031,0.0026</t>
-  </si>
-  <si>
-    <t>0.9733,0.0016,0.0407,0.0004</t>
-  </si>
-  <si>
-    <t>0.9918,0.0005,0.0130,0.0001</t>
-  </si>
-  <si>
-    <t>0.9139,0.0054,0.1034,0.0005</t>
-  </si>
-  <si>
-    <t>0.9406,0.0555,0.0019,0.0010</t>
-  </si>
-  <si>
-    <t>0.8942,0.1110,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.8708,0.1047,0.0035,0.0023</t>
-  </si>
-  <si>
-    <t>0.9609,0.0333,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.9157,0.0831,0.0020,0.0009</t>
-  </si>
-  <si>
-    <t>0.9438,0.0401,0.0021,0.0016</t>
-  </si>
-  <si>
-    <t>0.8930,0.0913,0.0026,0.0014</t>
-  </si>
-  <si>
-    <t>0.8976,0.0963,0.0077,0.0016</t>
-  </si>
-  <si>
-    <t>0.7654,0.1533,0.0903,0.0016</t>
-  </si>
-  <si>
-    <t>0.8773,0.0881,0.0167,0.0012</t>
-  </si>
-  <si>
-    <t>0.8520,0.1521,0.0195,0.0018</t>
-  </si>
-  <si>
-    <t>0.5889,0.0127,0.5200,0.0004</t>
-  </si>
-  <si>
-    <t>0.0400,0.0057,0.9746,0.0012</t>
-  </si>
-  <si>
-    <t>0.8012,0.1157,0.0648,0.0018</t>
-  </si>
-  <si>
-    <t>0.2114,0.0259,0.8129,0.0016</t>
-  </si>
-  <si>
-    <t>0.8819,0.0199,0.0755,0.0004</t>
-  </si>
-  <si>
-    <t>0.0441,0.0372,0.9369,0.0045</t>
-  </si>
-  <si>
-    <t>0.8925,0.0035,0.2282,0.0004</t>
-  </si>
-  <si>
-    <t>0.9789,0.0125,0.0045,0.0002</t>
-  </si>
-  <si>
-    <t>0.9771,0.0074,0.0053,0.0004</t>
-  </si>
-  <si>
-    <t>0.9749,0.0051,0.0145,0.0002</t>
-  </si>
-  <si>
-    <t>0.9729,0.0086,0.0065,0.0006</t>
-  </si>
-  <si>
-    <t>0.9412,0.0457,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.8016,0.1656,0.0038,0.0025</t>
-  </si>
-  <si>
-    <t>0.9143,0.1021,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.8930,0.1341,0.0030,0.0014</t>
-  </si>
-  <si>
-    <t>0.9197,0.0966,0.0020,0.0007</t>
-  </si>
-  <si>
-    <t>0.9191,0.0867,0.0027,0.0011</t>
-  </si>
-  <si>
-    <t>0.9465,0.0594,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.8210,0.2156,0.0060,0.0011</t>
-  </si>
-  <si>
-    <t>0.9958,0.0004,0.0038,0.0000</t>
-  </si>
-  <si>
-    <t>0.3841,0.0409,0.4738,0.0008</t>
-  </si>
-  <si>
-    <t>0.4530,0.0114,0.6345,0.0016</t>
-  </si>
-  <si>
-    <t>0.8322,0.0269,0.1945,0.0014</t>
-  </si>
-  <si>
-    <t>0.6256,0.0281,0.4244,0.0020</t>
-  </si>
-  <si>
-    <t>0.8383,0.0458,0.1129,0.0046</t>
-  </si>
-  <si>
-    <t>0.9876,0.0038,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.9673,0.0024,0.0439,0.0007</t>
-  </si>
-  <si>
-    <t>0.8798,0.1006,0.0146,0.0016</t>
-  </si>
-  <si>
-    <t>0.9438,0.0258,0.0125,0.0022</t>
-  </si>
-  <si>
-    <t>0.9705,0.0115,0.0021,0.0024</t>
-  </si>
-  <si>
-    <t>0.9851,0.0019,0.0011,0.0033</t>
-  </si>
-  <si>
-    <t>0.9621,0.0088,0.0036,0.0083</t>
-  </si>
-  <si>
-    <t>0.9587,0.0200,0.0132,0.0014</t>
+    <t>0.9217,0.0180,0.0174,0.0268</t>
+  </si>
+  <si>
+    <t>0.0253,0.0045,0.0003,0.9910</t>
+  </si>
+  <si>
+    <t>0.9230,0.0066,0.0006,0.0330</t>
+  </si>
+  <si>
+    <t>0.0521,0.0071,0.0006,0.9821</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9966,0.0008,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9942,0.0036,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9973,0.0015,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0010,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9289,0.0224,0.0400,0.0011</t>
+  </si>
+  <si>
+    <t>0.0274,0.0087,0.9749,0.0029</t>
+  </si>
+  <si>
+    <t>0.2735,0.0077,0.8659,0.0008</t>
+  </si>
+  <si>
+    <t>0.0545,0.0185,0.9246,0.0204</t>
+  </si>
+  <si>
+    <t>0.8993,0.0033,0.1355,0.0040</t>
+  </si>
+  <si>
+    <t>0.0104,0.9900,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.0037,0.9917,0.0023,0.0024</t>
+  </si>
+  <si>
+    <t>0.0648,0.9457,0.0102,0.0026</t>
+  </si>
+  <si>
+    <t>0.0102,0.9889,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.0016,0.9945,0.0114,0.0011</t>
+  </si>
+  <si>
+    <t>0.8272,0.0134,0.1931,0.0230</t>
+  </si>
+  <si>
+    <t>0.3839,0.0038,0.7452,0.0039</t>
+  </si>
+  <si>
+    <t>0.0064,0.0013,0.9919,0.0008</t>
+  </si>
+  <si>
+    <t>0.0481,0.0025,0.9641,0.0017</t>
+  </si>
+  <si>
+    <t>0.0447,0.0043,0.9679,0.0012</t>
+  </si>
+  <si>
+    <t>0.1771,0.0021,0.9222,0.0012</t>
+  </si>
+  <si>
+    <t>0.0037,0.0005,0.9943,0.0009</t>
+  </si>
+  <si>
+    <t>0.4853,0.6775,0.0041,0.0061</t>
+  </si>
+  <si>
+    <t>0.8049,0.1876,0.0314,0.0099</t>
+  </si>
+  <si>
+    <t>0.0043,0.0161,0.9923,0.0033</t>
+  </si>
+  <si>
+    <t>0.0019,0.9941,0.0091,0.0003</t>
+  </si>
+  <si>
+    <t>0.8830,0.0923,0.0254,0.0094</t>
+  </si>
+  <si>
+    <t>0.8810,0.0789,0.0432,0.0026</t>
+  </si>
+  <si>
+    <t>0.7520,0.3524,0.0085,0.0012</t>
+  </si>
+  <si>
+    <t>0.0241,0.9608,0.0874,0.0025</t>
+  </si>
+  <si>
+    <t>0.0202,0.5842,0.3911,0.0122</t>
+  </si>
+  <si>
+    <t>0.2285,0.0050,0.6720,0.0552</t>
+  </si>
+  <si>
+    <t>0.0301,0.0081,0.9721,0.0016</t>
+  </si>
+  <si>
+    <t>0.2453,0.0022,0.3550,0.2045</t>
+  </si>
+  <si>
+    <t>0.0061,0.3330,0.9875,0.0006</t>
+  </si>
+  <si>
+    <t>0.0032,0.9447,0.0477,0.0008</t>
+  </si>
+  <si>
+    <t>0.0388,0.0178,0.9504,0.0050</t>
+  </si>
+  <si>
+    <t>0.6338,0.1586,0.0129,0.1983</t>
+  </si>
+  <si>
+    <t>0.0019,0.9931,0.0019,0.0033</t>
+  </si>
+  <si>
+    <t>0.0127,0.9581,0.0462,0.0057</t>
+  </si>
+  <si>
+    <t>0.0060,0.9896,0.0146,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.0115,0.9925,0.0073</t>
+  </si>
+  <si>
+    <t>0.0003,0.0161,0.9972,0.0040</t>
+  </si>
+  <si>
+    <t>0.0114,0.0027,0.9836,0.0029</t>
+  </si>
+  <si>
+    <t>0.0179,0.0016,0.9795,0.0026</t>
+  </si>
+  <si>
+    <t>0.0039,0.0045,0.9912,0.0035</t>
+  </si>
+  <si>
+    <t>0.0017,0.0024,0.9922,0.0058</t>
+  </si>
+  <si>
+    <t>0.9709,0.0363,0.0014,0.0012</t>
+  </si>
+  <si>
+    <t>0.9820,0.0067,0.0058,0.0033</t>
+  </si>
+  <si>
+    <t>0.9983,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0123,0.0869,0.9881,0.0013</t>
+  </si>
+  <si>
+    <t>0.9949,0.0009,0.0007,0.0020</t>
+  </si>
+  <si>
+    <t>0.9975,0.0011,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0021,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.0018,0.8981,0.9646,0.0016</t>
+  </si>
+  <si>
+    <t>0.0055,0.0103,0.9900,0.0033</t>
+  </si>
+  <si>
+    <t>0.0044,0.4745,0.9796,0.0051</t>
+  </si>
+  <si>
+    <t>0.0001,0.9932,0.9844,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0010,0.9964,0.0007</t>
+  </si>
+  <si>
+    <t>0.0192,0.9705,0.0155,0.0005</t>
+  </si>
+  <si>
+    <t>0.0036,0.9959,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9630,0.0074,0.0316,0.0035</t>
+  </si>
+  <si>
+    <t>0.7348,0.0747,0.2259,0.0028</t>
+  </si>
+  <si>
+    <t>0.0049,0.0256,0.9903,0.0074</t>
+  </si>
+  <si>
+    <t>0.0008,0.9693,0.9621,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.9618,0.9256,0.0013</t>
+  </si>
+  <si>
+    <t>0.0041,0.9919,0.0394,0.0005</t>
+  </si>
+  <si>
+    <t>0.0051,0.9686,0.2808,0.0008</t>
+  </si>
+  <si>
+    <t>0.0042,0.0003,0.0023,0.9964</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.0002,0.9995</t>
+  </si>
+  <si>
+    <t>0.0026,0.0028,0.0001,0.9988</t>
+  </si>
+  <si>
+    <t>0.0213,0.0039,0.0010,0.9919</t>
+  </si>
+  <si>
+    <t>0.0015,0.0040,0.0017,0.9977</t>
+  </si>
+  <si>
+    <t>0.0009,0.0133,0.0002,0.9987</t>
+  </si>
+  <si>
+    <t>0.0061,0.9252,0.8434,0.0057</t>
+  </si>
+  <si>
+    <t>0.0113,0.5413,0.9610,0.0015</t>
+  </si>
+  <si>
+    <t>0.0023,0.7640,0.8436,0.0020</t>
+  </si>
+  <si>
+    <t>0.0015,0.8023,0.9909,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.9872,0.9308,0.0002</t>
+  </si>
+  <si>
+    <t>0.0135,0.5699,0.7401,0.0015</t>
+  </si>
+  <si>
+    <t>0.9953,0.0004,0.0003,0.0030</t>
+  </si>
+  <si>
+    <t>0.9931,0.0025,0.0033,0.0004</t>
+  </si>
+  <si>
+    <t>0.9912,0.0089,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9946,0.0028,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0006,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9964,0.0011,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0020,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9962,0.0006,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9984,0.0000,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0000,0.0019</t>
+  </si>
+  <si>
+    <t>0.9957,0.0003,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9974,0.0016,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0111,0.0115,0.9850,0.0019</t>
+  </si>
+  <si>
+    <t>0.0022,0.0019,0.9930,0.0033</t>
+  </si>
+  <si>
+    <t>0.9449,0.0044,0.0330,0.0114</t>
+  </si>
+  <si>
+    <t>0.0088,0.0038,0.9812,0.0074</t>
+  </si>
+  <si>
+    <t>0.0183,0.9845,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.0016,0.9955,0.0045,0.0004</t>
+  </si>
+  <si>
+    <t>0.0110,0.9861,0.0022,0.0018</t>
+  </si>
+  <si>
+    <t>0.0076,0.9912,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.0034,0.9940,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.0074,0.9856,0.0215,0.0010</t>
+  </si>
+  <si>
+    <t>0.3965,0.8156,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.8370,0.0319,0.1560,0.0117</t>
+  </si>
+  <si>
+    <t>0.0242,0.0019,0.9775,0.0031</t>
+  </si>
+  <si>
+    <t>0.4913,0.1307,0.3621,0.0582</t>
+  </si>
+  <si>
+    <t>0.1805,0.0085,0.8565,0.0073</t>
+  </si>
+  <si>
+    <t>0.1110,0.1205,0.1263,0.7746</t>
+  </si>
+  <si>
+    <t>0.0012,0.9957,0.0028,0.0011</t>
+  </si>
+  <si>
+    <t>0.0057,0.9866,0.0038,0.0029</t>
+  </si>
+  <si>
+    <t>0.0017,0.9955,0.0021,0.0006</t>
+  </si>
+  <si>
+    <t>0.0040,0.5934,0.9304,0.0016</t>
+  </si>
+  <si>
+    <t>0.0090,0.9857,0.0113,0.0002</t>
+  </si>
+  <si>
+    <t>0.9412,0.0287,0.0241,0.0085</t>
+  </si>
+  <si>
+    <t>0.9531,0.0435,0.0102,0.0007</t>
+  </si>
+  <si>
+    <t>0.9977,0.0008,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9963,0.0004,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9950,0.0009,0.0019,0.0008</t>
+  </si>
+  <si>
+    <t>0.9925,0.0014,0.0027,0.0012</t>
+  </si>
+  <si>
+    <t>0.9976,0.0000,0.0000,0.0026</t>
+  </si>
+  <si>
+    <t>0.9948,0.0005,0.0052,0.0005</t>
+  </si>
+  <si>
+    <t>0.9962,0.0001,0.0005,0.0023</t>
+  </si>
+  <si>
+    <t>0.9940,0.0020,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.0062,0.3971,0.9346,0.0149</t>
+  </si>
+  <si>
+    <t>0.0047,0.1710,0.9793,0.0016</t>
+  </si>
+  <si>
+    <t>0.0308,0.0480,0.9243,0.0042</t>
+  </si>
+  <si>
+    <t>0.0506,0.0117,0.9346,0.0159</t>
+  </si>
+  <si>
+    <t>0.9938,0.0005,0.0032,0.0005</t>
+  </si>
+  <si>
+    <t>0.6563,0.0140,0.3968,0.0105</t>
+  </si>
+  <si>
+    <t>0.2780,0.0036,0.8348,0.0016</t>
+  </si>
+  <si>
+    <t>0.6352,0.0870,0.2940,0.0167</t>
+  </si>
+  <si>
+    <t>0.0483,0.0001,0.0000,0.9931</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.0079,0.9985</t>
+  </si>
+  <si>
+    <t>0.0005,0.0029,0.0005,0.9991</t>
+  </si>
+  <si>
+    <t>0.0107,0.0001,0.0002,0.9973</t>
+  </si>
+  <si>
+    <t>0.0028,0.9737,0.2593,0.0029</t>
+  </si>
+  <si>
+    <t>0.9968,0.0004,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.2240,0.7927,0.0017,0.0209</t>
+  </si>
+  <si>
+    <t>0.9914,0.0027,0.0017,0.0016</t>
+  </si>
+  <si>
+    <t>0.1767,0.8838,0.0024,0.0030</t>
+  </si>
+  <si>
+    <t>0.9946,0.0003,0.0004,0.0023</t>
+  </si>
+  <si>
+    <t>0.3189,0.0043,0.0021,0.8247</t>
+  </si>
+  <si>
+    <t>0.9934,0.0018,0.0032,0.0005</t>
+  </si>
+  <si>
+    <t>0.0079,0.0545,0.8702,0.3673</t>
+  </si>
+  <si>
+    <t>0.9569,0.0001,0.0001,0.1180</t>
+  </si>
+  <si>
+    <t>0.9721,0.0005,0.0002,0.0364</t>
+  </si>
+  <si>
+    <t>0.1767,0.8011,0.0726,0.0267</t>
+  </si>
+  <si>
+    <t>0.9722,0.0145,0.0047,0.0024</t>
+  </si>
+  <si>
+    <t>0.9941,0.0009,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.7719,0.1899,0.0642,0.0061</t>
+  </si>
+  <si>
+    <t>0.8139,0.1873,0.0201,0.0100</t>
+  </si>
+  <si>
+    <t>0.9762,0.0193,0.0036,0.0008</t>
+  </si>
+  <si>
+    <t>0.9958,0.0009,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9917,0.0012,0.0016,0.0034</t>
+  </si>
+  <si>
+    <t>0.9863,0.0001,0.0004,0.0214</t>
+  </si>
+  <si>
+    <t>0.9960,0.0003,0.0004,0.0026</t>
+  </si>
+  <si>
+    <t>0.9883,0.0042,0.0019,0.0021</t>
+  </si>
+  <si>
+    <t>0.9785,0.0036,0.0119,0.0037</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.8120,0.2132,0.0021,0.0053</t>
+  </si>
+  <si>
+    <t>0.7824,0.2982,0.0050,0.0022</t>
+  </si>
+  <si>
+    <t>0.9060,0.1214,0.0031,0.0015</t>
+  </si>
+  <si>
+    <t>0.6719,0.2815,0.1066,0.0042</t>
+  </si>
+  <si>
+    <t>0.9912,0.0076,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9710,0.0097,0.0116,0.0046</t>
+  </si>
+  <si>
+    <t>0.9967,0.0004,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.8879,0.2084,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.0015,0.0160,0.9975,0.0015</t>
+  </si>
+  <si>
+    <t>0.9653,0.0171,0.0114,0.0024</t>
+  </si>
+  <si>
+    <t>0.0020,0.0020,0.9940,0.0020</t>
+  </si>
+  <si>
+    <t>0.0012,0.3372,0.9906,0.0029</t>
+  </si>
+  <si>
+    <t>0.0120,0.0235,0.9797,0.0062</t>
+  </si>
+  <si>
+    <t>0.0050,0.1483,0.9875,0.0024</t>
+  </si>
+  <si>
+    <t>0.0092,0.0052,0.9849,0.0023</t>
+  </si>
+  <si>
+    <t>0.0086,0.0035,0.9855,0.0027</t>
+  </si>
+  <si>
+    <t>0.0039,0.0206,0.9899,0.0036</t>
+  </si>
+  <si>
+    <t>0.0190,0.0054,0.9603,0.0156</t>
+  </si>
+  <si>
+    <t>0.1740,0.0556,0.7898,0.0197</t>
+  </si>
+  <si>
+    <t>0.1344,0.0221,0.8451,0.0091</t>
+  </si>
+  <si>
+    <t>0.1282,0.1721,0.6901,0.0024</t>
+  </si>
+  <si>
+    <t>0.2939,0.1447,0.4396,0.0038</t>
+  </si>
+  <si>
+    <t>0.3683,0.0102,0.7494,0.0015</t>
+  </si>
+  <si>
+    <t>0.5428,0.0648,0.4949,0.0330</t>
+  </si>
+  <si>
+    <t>0.2165,0.0611,0.7532,0.0218</t>
+  </si>
+  <si>
+    <t>0.0486,0.9691,0.0027,0.0009</t>
+  </si>
+  <si>
+    <t>0.0366,0.9841,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.3712,0.8014,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9951,0.0035,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.6884,0.4451,0.0067,0.0040</t>
+  </si>
+  <si>
+    <t>0.6559,0.2382,0.0384,0.0023</t>
+  </si>
+  <si>
+    <t>0.9172,0.0026,0.1313,0.0017</t>
+  </si>
+  <si>
+    <t>0.8597,0.0133,0.1122,0.0253</t>
+  </si>
+  <si>
+    <t>0.7313,0.0265,0.2469,0.0174</t>
+  </si>
+  <si>
+    <t>0.5532,0.0015,0.0627,0.2207</t>
+  </si>
+  <si>
+    <t>0.0035,0.0026,0.9921,0.0023</t>
+  </si>
+  <si>
+    <t>0.0163,0.1004,0.9028,0.0433</t>
+  </si>
+  <si>
+    <t>0.0200,0.0520,0.9610,0.0068</t>
+  </si>
+  <si>
+    <t>0.0225,0.0126,0.9573,0.0062</t>
+  </si>
+  <si>
+    <t>0.0466,0.3136,0.5573,0.0278</t>
+  </si>
+  <si>
+    <t>0.9901,0.0042,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9961,0.0006,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9956,0.0022,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9956,0.0010,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.9944,0.0027,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9859,0.0163,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9944,0.0010,0.0010,0.0024</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.0047,0.2069,0.9884,0.0015</t>
+  </si>
+  <si>
+    <t>0.0173,0.6396,0.8158,0.0039</t>
+  </si>
+  <si>
+    <t>0.8849,0.0171,0.0707,0.0180</t>
+  </si>
+  <si>
+    <t>0.0149,0.0023,0.9936,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0024,0.9969,0.0028</t>
+  </si>
+  <si>
+    <t>0.0009,0.7869,0.9867,0.0011</t>
+  </si>
+  <si>
+    <t>0.0024,0.0019,0.9976,0.0002</t>
+  </si>
+  <si>
+    <t>0.0080,0.0104,0.9642,0.0174</t>
+  </si>
+  <si>
+    <t>0.0020,0.0031,0.9954,0.0017</t>
+  </si>
+  <si>
+    <t>0.0436,0.0166,0.9449,0.0091</t>
+  </si>
+  <si>
+    <t>0.1489,0.0239,0.8209,0.0249</t>
+  </si>
+  <si>
+    <t>0.8914,0.0038,0.1133,0.0105</t>
+  </si>
+  <si>
+    <t>0.5724,0.0037,0.4023,0.0284</t>
+  </si>
+  <si>
+    <t>0.9886,0.0009,0.0058,0.0010</t>
+  </si>
+  <si>
+    <t>0.9923,0.0050,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9940,0.0039,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9945,0.0025,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.0237,0.0128,0.9582,0.0008</t>
+  </si>
+  <si>
+    <t>0.0015,0.0196,0.9954,0.0007</t>
+  </si>
+  <si>
+    <t>0.0308,0.0247,0.9255,0.0070</t>
+  </si>
+  <si>
+    <t>0.0219,0.0909,0.8577,0.0890</t>
+  </si>
+  <si>
+    <t>0.0060,0.0019,0.9922,0.0011</t>
+  </si>
+  <si>
+    <t>0.0714,0.0353,0.8497,0.0947</t>
+  </si>
+  <si>
+    <t>0.0847,0.0191,0.9011,0.0177</t>
+  </si>
+  <si>
+    <t>0.0450,0.0043,0.9519,0.0069</t>
+  </si>
+  <si>
+    <t>0.4146,0.0004,0.0009,0.8187</t>
+  </si>
+  <si>
+    <t>0.0133,0.0158,0.0031,0.9901</t>
+  </si>
+  <si>
+    <t>0.0389,0.0003,0.0009,0.9893</t>
+  </si>
+  <si>
+    <t>0.0019,0.0002,0.0004,0.9988</t>
+  </si>
+  <si>
+    <t>0.0013,0.0006,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.9902,0.0004,0.0024,0.0026</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
         <v>295</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4445,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
         <v>442</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5439,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
         <v>513</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
